--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8409,0.1009,0.0693,0.0030</t>
-  </si>
-  <si>
-    <t>0.7886,0.0593,0.0416,0.0261</t>
-  </si>
-  <si>
-    <t>0.8396,0.0920,0.0580,0.0026</t>
-  </si>
-  <si>
-    <t>0.8657,0.0429,0.0758,0.0027</t>
-  </si>
-  <si>
-    <t>0.5717,0.2142,0.0602,0.0166</t>
-  </si>
-  <si>
-    <t>0.6216,0.0509,0.0285,0.0867</t>
-  </si>
-  <si>
-    <t>0.7213,0.1515,0.0474,0.0118</t>
-  </si>
-  <si>
-    <t>0.8079,0.0267,0.0192,0.0423</t>
-  </si>
-  <si>
-    <t>0.7940,0.0383,0.0242,0.0271</t>
-  </si>
-  <si>
-    <t>0.7240,0.0586,0.0337,0.0348</t>
-  </si>
-  <si>
-    <t>0.7639,0.1221,0.0604,0.0091</t>
-  </si>
-  <si>
-    <t>0.7458,0.0765,0.0466,0.0208</t>
-  </si>
-  <si>
-    <t>0.8953,0.0458,0.0636,0.0005</t>
-  </si>
-  <si>
-    <t>0.5358,0.3812,0.1542,0.0011</t>
-  </si>
-  <si>
-    <t>0.8461,0.0754,0.0957,0.0004</t>
-  </si>
-  <si>
-    <t>0.9119,0.0187,0.0756,0.0004</t>
-  </si>
-  <si>
-    <t>0.8759,0.0458,0.0867,0.0010</t>
-  </si>
-  <si>
-    <t>0.0451,0.9606,0.1227,0.0013</t>
-  </si>
-  <si>
-    <t>0.4724,0.4977,0.1459,0.0059</t>
-  </si>
-  <si>
-    <t>0.8228,0.1360,0.0477,0.0012</t>
-  </si>
-  <si>
-    <t>0.4775,0.6172,0.0731,0.0021</t>
-  </si>
-  <si>
-    <t>0.2067,0.8321,0.1872,0.0008</t>
-  </si>
-  <si>
-    <t>0.9351,0.0145,0.0307,0.0011</t>
-  </si>
-  <si>
-    <t>0.8257,0.0455,0.1312,0.0005</t>
-  </si>
-  <si>
-    <t>0.7335,0.0317,0.3027,0.0010</t>
-  </si>
-  <si>
-    <t>0.8229,0.0297,0.1682,0.0004</t>
-  </si>
-  <si>
-    <t>0.9558,0.0069,0.0344,0.0002</t>
-  </si>
-  <si>
-    <t>0.7856,0.0406,0.2164,0.0030</t>
-  </si>
-  <si>
-    <t>0.4134,0.1013,0.6024,0.0072</t>
-  </si>
-  <si>
-    <t>0.7913,0.2543,0.0359,0.0016</t>
-  </si>
-  <si>
-    <t>0.8814,0.0407,0.0491,0.0029</t>
-  </si>
-  <si>
-    <t>0.0505,0.4458,0.9091,0.0038</t>
-  </si>
-  <si>
-    <t>0.7232,0.1030,0.2383,0.0023</t>
-  </si>
-  <si>
-    <t>0.7538,0.1527,0.0695,0.0081</t>
-  </si>
-  <si>
-    <t>0.7583,0.1106,0.1400,0.0054</t>
-  </si>
-  <si>
-    <t>0.9050,0.0512,0.0212,0.0022</t>
-  </si>
-  <si>
-    <t>0.9332,0.0686,0.0115,0.0002</t>
-  </si>
-  <si>
-    <t>0.8309,0.0113,0.1695,0.0006</t>
-  </si>
-  <si>
-    <t>0.9326,0.0014,0.0904,0.0002</t>
-  </si>
-  <si>
-    <t>0.9222,0.0105,0.0683,0.0002</t>
-  </si>
-  <si>
-    <t>0.9625,0.0037,0.0253,0.0002</t>
-  </si>
-  <si>
-    <t>0.9137,0.0074,0.1119,0.0004</t>
-  </si>
-  <si>
-    <t>0.4786,0.4473,0.0635,0.0004</t>
-  </si>
-  <si>
-    <t>0.9750,0.0022,0.0191,0.0001</t>
-  </si>
-  <si>
-    <t>0.6847,0.4153,0.0388,0.0013</t>
-  </si>
-  <si>
-    <t>0.8178,0.2997,0.0136,0.0002</t>
-  </si>
-  <si>
-    <t>0.5015,0.6664,0.0495,0.0002</t>
-  </si>
-  <si>
-    <t>0.1839,0.8797,0.0547,0.0003</t>
-  </si>
-  <si>
-    <t>0.3731,0.0814,0.4961,0.0003</t>
-  </si>
-  <si>
-    <t>0.4419,0.0334,0.6525,0.0020</t>
-  </si>
-  <si>
-    <t>0.7402,0.0244,0.3132,0.0015</t>
-  </si>
-  <si>
-    <t>0.6168,0.0215,0.4797,0.0003</t>
-  </si>
-  <si>
-    <t>0.0293,0.1557,0.9576,0.0003</t>
-  </si>
-  <si>
-    <t>0.8590,0.0156,0.1569,0.0004</t>
-  </si>
-  <si>
-    <t>0.6219,0.2248,0.0868,0.0115</t>
-  </si>
-  <si>
-    <t>0.8184,0.0375,0.0297,0.0142</t>
-  </si>
-  <si>
-    <t>0.8120,0.1188,0.0569,0.0042</t>
-  </si>
-  <si>
-    <t>0.5529,0.1008,0.4959,0.0031</t>
-  </si>
-  <si>
-    <t>0.7655,0.1001,0.0184,0.0063</t>
-  </si>
-  <si>
-    <t>0.6814,0.1244,0.0561,0.0294</t>
-  </si>
-  <si>
-    <t>0.8818,0.0233,0.0257,0.0107</t>
-  </si>
-  <si>
-    <t>0.3089,0.1991,0.4339,0.0002</t>
-  </si>
-  <si>
-    <t>0.3320,0.0639,0.6322,0.0001</t>
-  </si>
-  <si>
-    <t>0.5004,0.1358,0.3465,0.0010</t>
-  </si>
-  <si>
-    <t>0.0851,0.7690,0.4007,0.0002</t>
-  </si>
-  <si>
-    <t>0.2181,0.0282,0.8782,0.0009</t>
-  </si>
-  <si>
-    <t>0.7476,0.2734,0.0458,0.0007</t>
-  </si>
-  <si>
-    <t>0.0178,0.9898,0.0156,0.0002</t>
-  </si>
-  <si>
-    <t>0.9085,0.0567,0.0261,0.0009</t>
-  </si>
-  <si>
-    <t>0.8291,0.1129,0.0743,0.0013</t>
-  </si>
-  <si>
-    <t>0.1291,0.7916,0.3196,0.0041</t>
-  </si>
-  <si>
-    <t>0.4749,0.3912,0.0950,0.0000</t>
-  </si>
-  <si>
-    <t>0.9001,0.0153,0.1099,0.0001</t>
-  </si>
-  <si>
-    <t>0.3297,0.7539,0.0174,0.0001</t>
-  </si>
-  <si>
-    <t>0.5645,0.1177,0.1901,0.0002</t>
-  </si>
-  <si>
-    <t>0.9148,0.0150,0.0402,0.0020</t>
-  </si>
-  <si>
-    <t>0.8769,0.0270,0.0078,0.0163</t>
-  </si>
-  <si>
-    <t>0.8982,0.0366,0.0387,0.0023</t>
-  </si>
-  <si>
-    <t>0.9152,0.0351,0.0230,0.0033</t>
-  </si>
-  <si>
-    <t>0.8785,0.0658,0.0307,0.0032</t>
-  </si>
-  <si>
-    <t>0.9521,0.0229,0.0137,0.0006</t>
-  </si>
-  <si>
-    <t>0.0911,0.8593,0.3242,0.0006</t>
-  </si>
-  <si>
-    <t>0.6972,0.0438,0.2472,0.0001</t>
-  </si>
-  <si>
-    <t>0.8539,0.0408,0.1161,0.0003</t>
-  </si>
-  <si>
-    <t>0.7760,0.0247,0.2564,0.0002</t>
-  </si>
-  <si>
-    <t>0.1455,0.7067,0.2529,0.0001</t>
-  </si>
-  <si>
-    <t>0.4727,0.3454,0.2186,0.0007</t>
-  </si>
-  <si>
-    <t>0.8116,0.0336,0.0307,0.0233</t>
-  </si>
-  <si>
-    <t>0.8751,0.0632,0.0209,0.0036</t>
-  </si>
-  <si>
-    <t>0.8603,0.0306,0.0229,0.0144</t>
-  </si>
-  <si>
-    <t>0.7850,0.0988,0.0350,0.0088</t>
-  </si>
-  <si>
-    <t>0.8848,0.0229,0.0227,0.0088</t>
-  </si>
-  <si>
-    <t>0.6979,0.1309,0.0770,0.0149</t>
-  </si>
-  <si>
-    <t>0.6160,0.0806,0.0627,0.0667</t>
-  </si>
-  <si>
-    <t>0.7167,0.1083,0.0435,0.0148</t>
-  </si>
-  <si>
-    <t>0.8297,0.0291,0.0296,0.0220</t>
-  </si>
-  <si>
-    <t>0.8809,0.0249,0.0110,0.0107</t>
-  </si>
-  <si>
-    <t>0.7564,0.0926,0.0277,0.0123</t>
-  </si>
-  <si>
-    <t>0.7282,0.1056,0.0757,0.0177</t>
-  </si>
-  <si>
-    <t>0.7823,0.0999,0.0289,0.0115</t>
-  </si>
-  <si>
-    <t>0.6490,0.1659,0.0639,0.0261</t>
-  </si>
-  <si>
-    <t>0.6597,0.1169,0.0581,0.0280</t>
-  </si>
-  <si>
-    <t>0.6733,0.1700,0.0950,0.0113</t>
-  </si>
-  <si>
-    <t>0.0609,0.1044,0.9524,0.0015</t>
-  </si>
-  <si>
-    <t>0.8898,0.0318,0.0842,0.0004</t>
-  </si>
-  <si>
-    <t>0.9555,0.0086,0.0338,0.0002</t>
-  </si>
-  <si>
-    <t>0.9146,0.0140,0.0662,0.0004</t>
-  </si>
-  <si>
-    <t>0.2126,0.8423,0.1237,0.0010</t>
-  </si>
-  <si>
-    <t>0.6015,0.2797,0.2001,0.0059</t>
-  </si>
-  <si>
-    <t>0.3598,0.6590,0.1282,0.0048</t>
-  </si>
-  <si>
-    <t>0.4884,0.5600,0.0999,0.0052</t>
-  </si>
-  <si>
-    <t>0.4819,0.6394,0.0652,0.0020</t>
-  </si>
-  <si>
-    <t>0.0837,0.9427,0.0545,0.0023</t>
-  </si>
-  <si>
-    <t>0.5497,0.3915,0.1655,0.0037</t>
-  </si>
-  <si>
-    <t>0.9158,0.0392,0.0284,0.0012</t>
-  </si>
-  <si>
-    <t>0.9460,0.0080,0.0335,0.0006</t>
-  </si>
-  <si>
-    <t>0.8860,0.0289,0.0874,0.0018</t>
-  </si>
-  <si>
-    <t>0.8841,0.0684,0.0439,0.0008</t>
-  </si>
-  <si>
-    <t>0.9438,0.0215,0.0154,0.0009</t>
-  </si>
-  <si>
-    <t>0.1886,0.8803,0.0610,0.0001</t>
-  </si>
-  <si>
-    <t>0.4394,0.5985,0.1040,0.0004</t>
-  </si>
-  <si>
-    <t>0.7237,0.3583,0.0452,0.0003</t>
-  </si>
-  <si>
-    <t>0.0564,0.8647,0.5557,0.0007</t>
-  </si>
-  <si>
-    <t>0.4759,0.5888,0.1212,0.0026</t>
-  </si>
-  <si>
-    <t>0.8450,0.0929,0.0546,0.0035</t>
-  </si>
-  <si>
-    <t>0.6243,0.2879,0.1106,0.0065</t>
-  </si>
-  <si>
-    <t>0.7393,0.1390,0.0416,0.0122</t>
-  </si>
-  <si>
-    <t>0.8497,0.0370,0.0415,0.0114</t>
-  </si>
-  <si>
-    <t>0.9169,0.0246,0.0130,0.0038</t>
-  </si>
-  <si>
-    <t>0.8535,0.0732,0.0345,0.0039</t>
-  </si>
-  <si>
-    <t>0.7337,0.0436,0.0408,0.0506</t>
-  </si>
-  <si>
-    <t>0.8351,0.0510,0.0493,0.0065</t>
-  </si>
-  <si>
-    <t>0.7318,0.0618,0.0697,0.0309</t>
-  </si>
-  <si>
-    <t>0.7088,0.1416,0.1218,0.0134</t>
-  </si>
-  <si>
-    <t>0.8212,0.0480,0.0706,0.0001</t>
-  </si>
-  <si>
-    <t>0.5973,0.0357,0.3826,0.0002</t>
-  </si>
-  <si>
-    <t>0.8800,0.0120,0.1182,0.0001</t>
-  </si>
-  <si>
-    <t>0.9100,0.0080,0.0954,0.0001</t>
-  </si>
-  <si>
-    <t>0.9178,0.0268,0.0458,0.0004</t>
-  </si>
-  <si>
-    <t>0.8268,0.1721,0.0457,0.0005</t>
-  </si>
-  <si>
-    <t>0.8182,0.0489,0.1718,0.0006</t>
-  </si>
-  <si>
-    <t>0.8166,0.1207,0.0714,0.0013</t>
-  </si>
-  <si>
-    <t>0.8632,0.1078,0.0284,0.0028</t>
-  </si>
-  <si>
-    <t>0.8532,0.0111,0.0244,0.0249</t>
-  </si>
-  <si>
-    <t>0.9102,0.0302,0.0232,0.0061</t>
-  </si>
-  <si>
-    <t>0.8941,0.0273,0.0457,0.0024</t>
-  </si>
-  <si>
-    <t>0.3484,0.4479,0.2561,0.0070</t>
-  </si>
-  <si>
-    <t>0.6978,0.1185,0.0650,0.0220</t>
-  </si>
-  <si>
-    <t>0.5963,0.2543,0.1031,0.0127</t>
-  </si>
-  <si>
-    <t>0.8107,0.0539,0.0671,0.0147</t>
-  </si>
-  <si>
-    <t>0.7431,0.2053,0.0448,0.0042</t>
-  </si>
-  <si>
-    <t>0.8516,0.1117,0.0541,0.0009</t>
-  </si>
-  <si>
-    <t>0.7296,0.1999,0.0921,0.0044</t>
-  </si>
-  <si>
-    <t>0.7440,0.0541,0.0284,0.0210</t>
-  </si>
-  <si>
-    <t>0.0931,0.4648,0.8451,0.0108</t>
-  </si>
-  <si>
-    <t>0.9343,0.0230,0.0122,0.0022</t>
-  </si>
-  <si>
-    <t>0.6159,0.0380,0.0218,0.1231</t>
-  </si>
-  <si>
-    <t>0.7493,0.2131,0.0856,0.0010</t>
-  </si>
-  <si>
-    <t>0.7104,0.1952,0.0735,0.0043</t>
-  </si>
-  <si>
-    <t>0.9142,0.0573,0.0245,0.0005</t>
-  </si>
-  <si>
-    <t>0.7499,0.2191,0.0553,0.0028</t>
-  </si>
-  <si>
-    <t>0.8226,0.0952,0.0611,0.0025</t>
-  </si>
-  <si>
-    <t>0.9034,0.0566,0.0268,0.0012</t>
-  </si>
-  <si>
-    <t>0.7141,0.0904,0.0911,0.0197</t>
-  </si>
-  <si>
-    <t>0.7646,0.1350,0.0498,0.0120</t>
-  </si>
-  <si>
-    <t>0.7823,0.0896,0.0597,0.0122</t>
-  </si>
-  <si>
-    <t>0.8555,0.0528,0.0334,0.0048</t>
-  </si>
-  <si>
-    <t>0.8193,0.0557,0.0343,0.0122</t>
-  </si>
-  <si>
-    <t>0.8345,0.0348,0.0546,0.0133</t>
-  </si>
-  <si>
-    <t>0.7568,0.1026,0.0432,0.0115</t>
-  </si>
-  <si>
-    <t>0.6922,0.1137,0.0773,0.0198</t>
-  </si>
-  <si>
-    <t>0.8328,0.1301,0.0352,0.0020</t>
-  </si>
-  <si>
-    <t>0.7194,0.2452,0.0784,0.0029</t>
-  </si>
-  <si>
-    <t>0.7967,0.1175,0.0668,0.0030</t>
-  </si>
-  <si>
-    <t>0.9004,0.0349,0.0092,0.0032</t>
-  </si>
-  <si>
-    <t>0.8521,0.1005,0.0445,0.0015</t>
-  </si>
-  <si>
-    <t>0.5839,0.3593,0.1114,0.0044</t>
-  </si>
-  <si>
-    <t>0.6828,0.1007,0.0780,0.0326</t>
-  </si>
-  <si>
-    <t>0.8166,0.0855,0.0347,0.0082</t>
-  </si>
-  <si>
-    <t>0.1133,0.0859,0.9254,0.0007</t>
-  </si>
-  <si>
-    <t>0.6174,0.1874,0.1095,0.0144</t>
-  </si>
-  <si>
-    <t>0.5574,0.0401,0.5040,0.0004</t>
-  </si>
-  <si>
-    <t>0.9435,0.0034,0.0704,0.0001</t>
-  </si>
-  <si>
-    <t>0.8642,0.0280,0.1147,0.0003</t>
-  </si>
-  <si>
-    <t>0.0218,0.2506,0.9644,0.0004</t>
-  </si>
-  <si>
-    <t>0.8349,0.0094,0.2578,0.0002</t>
-  </si>
-  <si>
-    <t>0.8328,0.0100,0.1981,0.0002</t>
-  </si>
-  <si>
-    <t>0.7515,0.0386,0.2456,0.0004</t>
-  </si>
-  <si>
-    <t>0.8630,0.0215,0.1265,0.0005</t>
-  </si>
-  <si>
-    <t>0.7769,0.0915,0.1319,0.0003</t>
-  </si>
-  <si>
-    <t>0.7704,0.1219,0.1294,0.0012</t>
-  </si>
-  <si>
-    <t>0.8761,0.0452,0.0658,0.0004</t>
-  </si>
-  <si>
-    <t>0.6912,0.2769,0.0909,0.0009</t>
-  </si>
-  <si>
-    <t>0.9369,0.0264,0.0301,0.0004</t>
-  </si>
-  <si>
-    <t>0.9187,0.0615,0.0275,0.0003</t>
-  </si>
-  <si>
-    <t>0.7415,0.1674,0.1049,0.0022</t>
-  </si>
-  <si>
-    <t>0.6771,0.2718,0.0983,0.0063</t>
-  </si>
-  <si>
-    <t>0.6750,0.2382,0.0972,0.0053</t>
-  </si>
-  <si>
-    <t>0.8971,0.0366,0.0256,0.0030</t>
-  </si>
-  <si>
-    <t>0.4765,0.2677,0.0579,0.0220</t>
-  </si>
-  <si>
-    <t>0.8047,0.0747,0.0504,0.0089</t>
-  </si>
-  <si>
-    <t>0.9369,0.0194,0.0390,0.0003</t>
-  </si>
-  <si>
-    <t>0.8571,0.0361,0.1292,0.0006</t>
-  </si>
-  <si>
-    <t>0.9656,0.0111,0.0122,0.0006</t>
-  </si>
-  <si>
-    <t>0.9459,0.0103,0.0339,0.0001</t>
-  </si>
-  <si>
-    <t>0.8735,0.0180,0.1044,0.0014</t>
-  </si>
-  <si>
-    <t>0.6177,0.1185,0.3421,0.0016</t>
-  </si>
-  <si>
-    <t>0.8548,0.0379,0.0987,0.0002</t>
-  </si>
-  <si>
-    <t>0.8686,0.0190,0.1073,0.0002</t>
-  </si>
-  <si>
-    <t>0.8993,0.0086,0.1182,0.0001</t>
-  </si>
-  <si>
-    <t>0.9139,0.0159,0.0424,0.0001</t>
-  </si>
-  <si>
-    <t>0.7306,0.0741,0.0447,0.0307</t>
-  </si>
-  <si>
-    <t>0.6301,0.1458,0.0526,0.0184</t>
-  </si>
-  <si>
-    <t>0.7182,0.0717,0.0459,0.0248</t>
-  </si>
-  <si>
-    <t>0.7731,0.0396,0.0527,0.0355</t>
-  </si>
-  <si>
-    <t>0.7123,0.1757,0.0768,0.0077</t>
-  </si>
-  <si>
-    <t>0.8424,0.0506,0.0268,0.0104</t>
-  </si>
-  <si>
-    <t>0.7596,0.0351,0.0474,0.0358</t>
-  </si>
-  <si>
-    <t>0.7251,0.0885,0.0985,0.0124</t>
-  </si>
-  <si>
-    <t>0.6189,0.2069,0.2419,0.0013</t>
-  </si>
-  <si>
-    <t>0.7757,0.0872,0.0986,0.0042</t>
-  </si>
-  <si>
-    <t>0.7975,0.1357,0.0527,0.0036</t>
-  </si>
-  <si>
-    <t>0.8090,0.0056,0.3363,0.0001</t>
-  </si>
-  <si>
-    <t>0.4559,0.0397,0.6007,0.0020</t>
-  </si>
-  <si>
-    <t>0.8796,0.0284,0.0741,0.0002</t>
-  </si>
-  <si>
-    <t>0.2537,0.0048,0.9102,0.0002</t>
-  </si>
-  <si>
-    <t>0.9026,0.0206,0.0822,0.0008</t>
-  </si>
-  <si>
-    <t>0.0878,0.1255,0.8778,0.0003</t>
-  </si>
-  <si>
-    <t>0.7199,0.0093,0.4114,0.0001</t>
-  </si>
-  <si>
-    <t>0.6925,0.1480,0.1827,0.0029</t>
-  </si>
-  <si>
-    <t>0.9607,0.0098,0.0223,0.0001</t>
-  </si>
-  <si>
-    <t>0.9313,0.0243,0.0350,0.0007</t>
-  </si>
-  <si>
-    <t>0.9236,0.0497,0.0200,0.0011</t>
-  </si>
-  <si>
-    <t>0.7859,0.0794,0.0348,0.0098</t>
-  </si>
-  <si>
-    <t>0.7742,0.0727,0.0470,0.0132</t>
-  </si>
-  <si>
-    <t>0.8324,0.0250,0.0288,0.0181</t>
-  </si>
-  <si>
-    <t>0.7855,0.1089,0.1084,0.0037</t>
-  </si>
-  <si>
-    <t>0.6553,0.2245,0.0367,0.0074</t>
-  </si>
-  <si>
-    <t>0.8493,0.0409,0.0270,0.0122</t>
-  </si>
-  <si>
-    <t>0.7868,0.0656,0.0391,0.0134</t>
-  </si>
-  <si>
-    <t>0.7489,0.0349,0.0274,0.0407</t>
-  </si>
-  <si>
-    <t>0.7618,0.1555,0.0764,0.0008</t>
-  </si>
-  <si>
-    <t>0.6516,0.0467,0.2102,0.0001</t>
-  </si>
-  <si>
-    <t>0.5052,0.0403,0.5451,0.0033</t>
-  </si>
-  <si>
-    <t>0.9433,0.0088,0.0602,0.0001</t>
-  </si>
-  <si>
-    <t>0.4740,0.0780,0.5320,0.0008</t>
-  </si>
-  <si>
-    <t>0.9345,0.0150,0.0403,0.0005</t>
-  </si>
-  <si>
-    <t>0.8958,0.0115,0.1191,0.0002</t>
-  </si>
-  <si>
-    <t>0.9035,0.0174,0.0770,0.0006</t>
-  </si>
-  <si>
-    <t>0.6556,0.2496,0.1398,0.0062</t>
-  </si>
-  <si>
-    <t>0.9233,0.0194,0.0305,0.0018</t>
-  </si>
-  <si>
-    <t>0.9001,0.0319,0.0239,0.0057</t>
-  </si>
-  <si>
-    <t>0.8863,0.0194,0.0394,0.0097</t>
-  </si>
-  <si>
-    <t>0.8675,0.0316,0.0339,0.0095</t>
-  </si>
-  <si>
-    <t>0.8403,0.0589,0.0818,0.0030</t>
+    <t>0.8187,0.0973,0.0680,0.0045</t>
+  </si>
+  <si>
+    <t>0.8564,0.0252,0.0375,0.0133</t>
+  </si>
+  <si>
+    <t>0.7707,0.1209,0.0427,0.0114</t>
+  </si>
+  <si>
+    <t>0.8351,0.0497,0.0339,0.0116</t>
+  </si>
+  <si>
+    <t>0.6331,0.1031,0.0816,0.0353</t>
+  </si>
+  <si>
+    <t>0.6205,0.1350,0.0458,0.0265</t>
+  </si>
+  <si>
+    <t>0.8069,0.0655,0.0200,0.0098</t>
+  </si>
+  <si>
+    <t>0.7788,0.1083,0.0437,0.0086</t>
+  </si>
+  <si>
+    <t>0.7699,0.0746,0.0559,0.0140</t>
+  </si>
+  <si>
+    <t>0.8732,0.0452,0.0326,0.0065</t>
+  </si>
+  <si>
+    <t>0.6999,0.1695,0.0764,0.0110</t>
+  </si>
+  <si>
+    <t>0.6766,0.1428,0.0852,0.0188</t>
+  </si>
+  <si>
+    <t>0.8800,0.0486,0.0791,0.0006</t>
+  </si>
+  <si>
+    <t>0.8083,0.1405,0.0770,0.0011</t>
+  </si>
+  <si>
+    <t>0.8704,0.0234,0.1341,0.0004</t>
+  </si>
+  <si>
+    <t>0.8839,0.0129,0.1472,0.0002</t>
+  </si>
+  <si>
+    <t>0.9110,0.0384,0.0505,0.0002</t>
+  </si>
+  <si>
+    <t>0.0740,0.9511,0.0957,0.0005</t>
+  </si>
+  <si>
+    <t>0.4337,0.5977,0.1444,0.0025</t>
+  </si>
+  <si>
+    <t>0.7850,0.1512,0.0663,0.0033</t>
+  </si>
+  <si>
+    <t>0.4678,0.5910,0.1191,0.0026</t>
+  </si>
+  <si>
+    <t>0.3307,0.7675,0.1139,0.0012</t>
+  </si>
+  <si>
+    <t>0.9549,0.0178,0.0160,0.0005</t>
+  </si>
+  <si>
+    <t>0.9266,0.0075,0.0889,0.0002</t>
+  </si>
+  <si>
+    <t>0.6497,0.0546,0.3689,0.0012</t>
+  </si>
+  <si>
+    <t>0.9436,0.0247,0.0205,0.0002</t>
+  </si>
+  <si>
+    <t>0.9533,0.0179,0.0208,0.0001</t>
+  </si>
+  <si>
+    <t>0.9050,0.0098,0.0798,0.0012</t>
+  </si>
+  <si>
+    <t>0.5590,0.0137,0.6448,0.0003</t>
+  </si>
+  <si>
+    <t>0.3337,0.7614,0.0912,0.0007</t>
+  </si>
+  <si>
+    <t>0.9332,0.0338,0.0186,0.0012</t>
+  </si>
+  <si>
+    <t>0.1112,0.0991,0.9205,0.0021</t>
+  </si>
+  <si>
+    <t>0.8399,0.0756,0.1003,0.0007</t>
+  </si>
+  <si>
+    <t>0.6950,0.2338,0.0816,0.0039</t>
+  </si>
+  <si>
+    <t>0.6811,0.1423,0.1762,0.0116</t>
+  </si>
+  <si>
+    <t>0.7461,0.1366,0.0860,0.0090</t>
+  </si>
+  <si>
+    <t>0.8694,0.1223,0.0323,0.0004</t>
+  </si>
+  <si>
+    <t>0.7258,0.0629,0.2090,0.0009</t>
+  </si>
+  <si>
+    <t>0.9597,0.0020,0.0466,0.0001</t>
+  </si>
+  <si>
+    <t>0.9135,0.0182,0.0647,0.0001</t>
+  </si>
+  <si>
+    <t>0.9469,0.0033,0.0424,0.0003</t>
+  </si>
+  <si>
+    <t>0.8961,0.0129,0.1343,0.0001</t>
+  </si>
+  <si>
+    <t>0.3350,0.7107,0.0344,0.0003</t>
+  </si>
+  <si>
+    <t>0.8332,0.0104,0.2158,0.0004</t>
+  </si>
+  <si>
+    <t>0.9185,0.0599,0.0242,0.0014</t>
+  </si>
+  <si>
+    <t>0.4900,0.6937,0.0359,0.0006</t>
+  </si>
+  <si>
+    <t>0.6866,0.4449,0.0280,0.0002</t>
+  </si>
+  <si>
+    <t>0.0319,0.9638,0.1859,0.0010</t>
+  </si>
+  <si>
+    <t>0.7280,0.0494,0.1892,0.0009</t>
+  </si>
+  <si>
+    <t>0.5121,0.0250,0.6036,0.0012</t>
+  </si>
+  <si>
+    <t>0.9395,0.0104,0.0463,0.0003</t>
+  </si>
+  <si>
+    <t>0.8562,0.0209,0.1429,0.0011</t>
+  </si>
+  <si>
+    <t>0.5821,0.0413,0.4685,0.0004</t>
+  </si>
+  <si>
+    <t>0.8198,0.0043,0.3080,0.0001</t>
+  </si>
+  <si>
+    <t>0.5405,0.2769,0.1207,0.0237</t>
+  </si>
+  <si>
+    <t>0.6832,0.1473,0.1063,0.0109</t>
+  </si>
+  <si>
+    <t>0.8510,0.0274,0.0128,0.0151</t>
+  </si>
+  <si>
+    <t>0.1389,0.5323,0.7841,0.0055</t>
+  </si>
+  <si>
+    <t>0.8124,0.0663,0.0250,0.0083</t>
+  </si>
+  <si>
+    <t>0.7447,0.0674,0.0856,0.0179</t>
+  </si>
+  <si>
+    <t>0.7005,0.1495,0.0524,0.0148</t>
+  </si>
+  <si>
+    <t>0.0337,0.7088,0.7503,0.0002</t>
+  </si>
+  <si>
+    <t>0.6217,0.0604,0.2619,0.0004</t>
+  </si>
+  <si>
+    <t>0.8064,0.0046,0.3145,0.0002</t>
+  </si>
+  <si>
+    <t>0.1134,0.7441,0.3620,0.0002</t>
+  </si>
+  <si>
+    <t>0.6605,0.0343,0.3585,0.0007</t>
+  </si>
+  <si>
+    <t>0.8663,0.1661,0.0051,0.0006</t>
+  </si>
+  <si>
+    <t>0.0148,0.9867,0.0823,0.0001</t>
+  </si>
+  <si>
+    <t>0.9471,0.0445,0.0166,0.0002</t>
+  </si>
+  <si>
+    <t>0.8196,0.0571,0.0417,0.0078</t>
+  </si>
+  <si>
+    <t>0.0323,0.5414,0.9224,0.0019</t>
+  </si>
+  <si>
+    <t>0.6819,0.3108,0.0344,0.0001</t>
+  </si>
+  <si>
+    <t>0.2091,0.6762,0.2443,0.0004</t>
+  </si>
+  <si>
+    <t>0.2104,0.8177,0.0120,0.0000</t>
+  </si>
+  <si>
+    <t>0.0948,0.8608,0.0854,0.0001</t>
+  </si>
+  <si>
+    <t>0.8745,0.0407,0.0384,0.0053</t>
+  </si>
+  <si>
+    <t>0.9483,0.0169,0.0091,0.0023</t>
+  </si>
+  <si>
+    <t>0.9109,0.0577,0.0114,0.0032</t>
+  </si>
+  <si>
+    <t>0.9101,0.0338,0.0306,0.0028</t>
+  </si>
+  <si>
+    <t>0.9504,0.0136,0.0139,0.0015</t>
+  </si>
+  <si>
+    <t>0.6975,0.0366,0.0366,0.1135</t>
+  </si>
+  <si>
+    <t>0.1610,0.4485,0.4246,0.0002</t>
+  </si>
+  <si>
+    <t>0.2421,0.1428,0.6206,0.0002</t>
+  </si>
+  <si>
+    <t>0.5130,0.0469,0.4399,0.0001</t>
+  </si>
+  <si>
+    <t>0.7966,0.0189,0.2263,0.0002</t>
+  </si>
+  <si>
+    <t>0.1769,0.7592,0.1341,0.0001</t>
+  </si>
+  <si>
+    <t>0.7881,0.0327,0.1703,0.0001</t>
+  </si>
+  <si>
+    <t>0.5716,0.2872,0.0876,0.0120</t>
+  </si>
+  <si>
+    <t>0.7027,0.0679,0.0768,0.0348</t>
+  </si>
+  <si>
+    <t>0.7233,0.0719,0.0647,0.0207</t>
+  </si>
+  <si>
+    <t>0.8212,0.0446,0.0274,0.0137</t>
+  </si>
+  <si>
+    <t>0.7519,0.0882,0.0318,0.0166</t>
+  </si>
+  <si>
+    <t>0.6525,0.2804,0.0472,0.0060</t>
+  </si>
+  <si>
+    <t>0.7759,0.0739,0.0336,0.0182</t>
+  </si>
+  <si>
+    <t>0.9060,0.0239,0.0137,0.0046</t>
+  </si>
+  <si>
+    <t>0.8079,0.0659,0.0285,0.0091</t>
+  </si>
+  <si>
+    <t>0.7107,0.0995,0.0289,0.0223</t>
+  </si>
+  <si>
+    <t>0.7873,0.0488,0.0304,0.0161</t>
+  </si>
+  <si>
+    <t>0.7710,0.0264,0.0279,0.0472</t>
+  </si>
+  <si>
+    <t>0.7395,0.0722,0.0543,0.0169</t>
+  </si>
+  <si>
+    <t>0.8720,0.0270,0.0212,0.0095</t>
+  </si>
+  <si>
+    <t>0.8438,0.0431,0.0305,0.0087</t>
+  </si>
+  <si>
+    <t>0.8476,0.0146,0.0151,0.0274</t>
+  </si>
+  <si>
+    <t>0.5343,0.0175,0.6098,0.0005</t>
+  </si>
+  <si>
+    <t>0.8768,0.0074,0.1888,0.0002</t>
+  </si>
+  <si>
+    <t>0.9091,0.0325,0.0688,0.0006</t>
+  </si>
+  <si>
+    <t>0.9303,0.0137,0.0376,0.0006</t>
+  </si>
+  <si>
+    <t>0.5438,0.5441,0.0976,0.0025</t>
+  </si>
+  <si>
+    <t>0.5572,0.4819,0.1014,0.0017</t>
+  </si>
+  <si>
+    <t>0.6262,0.3417,0.0847,0.0039</t>
+  </si>
+  <si>
+    <t>0.6224,0.3068,0.0771,0.0078</t>
+  </si>
+  <si>
+    <t>0.6667,0.3265,0.0873,0.0033</t>
+  </si>
+  <si>
+    <t>0.1804,0.8673,0.1102,0.0019</t>
+  </si>
+  <si>
+    <t>0.6755,0.2216,0.1158,0.0057</t>
+  </si>
+  <si>
+    <t>0.8920,0.0375,0.0360,0.0024</t>
+  </si>
+  <si>
+    <t>0.8658,0.0256,0.1216,0.0003</t>
+  </si>
+  <si>
+    <t>0.9465,0.0147,0.0341,0.0003</t>
+  </si>
+  <si>
+    <t>0.8932,0.1092,0.0226,0.0005</t>
+  </si>
+  <si>
+    <t>0.9315,0.0309,0.0250,0.0006</t>
+  </si>
+  <si>
+    <t>0.2289,0.8684,0.0659,0.0004</t>
+  </si>
+  <si>
+    <t>0.0698,0.9601,0.1026,0.0006</t>
+  </si>
+  <si>
+    <t>0.7774,0.1451,0.0846,0.0019</t>
+  </si>
+  <si>
+    <t>0.0587,0.9303,0.1643,0.0003</t>
+  </si>
+  <si>
+    <t>0.8813,0.0843,0.0215,0.0016</t>
+  </si>
+  <si>
+    <t>0.7126,0.1746,0.0837,0.0069</t>
+  </si>
+  <si>
+    <t>0.8027,0.1242,0.0848,0.0033</t>
+  </si>
+  <si>
+    <t>0.8292,0.0834,0.0593,0.0064</t>
+  </si>
+  <si>
+    <t>0.8997,0.0230,0.0193,0.0077</t>
+  </si>
+  <si>
+    <t>0.8077,0.0897,0.0490,0.0075</t>
+  </si>
+  <si>
+    <t>0.8453,0.0453,0.0425,0.0110</t>
+  </si>
+  <si>
+    <t>0.7453,0.0645,0.0562,0.0368</t>
+  </si>
+  <si>
+    <t>0.8756,0.0453,0.0446,0.0021</t>
+  </si>
+  <si>
+    <t>0.7879,0.1436,0.0339,0.0048</t>
+  </si>
+  <si>
+    <t>0.7637,0.0718,0.0472,0.0229</t>
+  </si>
+  <si>
+    <t>0.0610,0.8952,0.1288,0.0003</t>
+  </si>
+  <si>
+    <t>0.6416,0.0307,0.3369,0.0002</t>
+  </si>
+  <si>
+    <t>0.6978,0.0064,0.5064,0.0001</t>
+  </si>
+  <si>
+    <t>0.8955,0.0057,0.1369,0.0001</t>
+  </si>
+  <si>
+    <t>0.9147,0.0493,0.0340,0.0002</t>
+  </si>
+  <si>
+    <t>0.8882,0.0844,0.0379,0.0002</t>
+  </si>
+  <si>
+    <t>0.7900,0.0397,0.2266,0.0016</t>
+  </si>
+  <si>
+    <t>0.8322,0.1266,0.0575,0.0010</t>
+  </si>
+  <si>
+    <t>0.9662,0.0104,0.0108,0.0003</t>
+  </si>
+  <si>
+    <t>0.9026,0.0168,0.0404,0.0048</t>
+  </si>
+  <si>
+    <t>0.6872,0.4135,0.0390,0.0016</t>
+  </si>
+  <si>
+    <t>0.8585,0.0301,0.0380,0.0123</t>
+  </si>
+  <si>
+    <t>0.2228,0.3771,0.4897,0.0005</t>
+  </si>
+  <si>
+    <t>0.7403,0.0971,0.1051,0.0164</t>
+  </si>
+  <si>
+    <t>0.7030,0.2649,0.0794,0.0042</t>
+  </si>
+  <si>
+    <t>0.7097,0.1348,0.0412,0.0113</t>
+  </si>
+  <si>
+    <t>0.8013,0.1073,0.0419,0.0068</t>
+  </si>
+  <si>
+    <t>0.9085,0.0209,0.0393,0.0027</t>
+  </si>
+  <si>
+    <t>0.8044,0.1076,0.0657,0.0028</t>
+  </si>
+  <si>
+    <t>0.6956,0.1669,0.0374,0.0107</t>
+  </si>
+  <si>
+    <t>0.0263,0.6981,0.8953,0.0126</t>
+  </si>
+  <si>
+    <t>0.7605,0.1436,0.0313,0.0117</t>
+  </si>
+  <si>
+    <t>0.6105,0.1825,0.1324,0.0286</t>
+  </si>
+  <si>
+    <t>0.7042,0.2253,0.1270,0.0018</t>
+  </si>
+  <si>
+    <t>0.8306,0.0928,0.0734,0.0022</t>
+  </si>
+  <si>
+    <t>0.8855,0.0668,0.0197,0.0013</t>
+  </si>
+  <si>
+    <t>0.8952,0.0615,0.0334,0.0007</t>
+  </si>
+  <si>
+    <t>0.7813,0.1795,0.0703,0.0027</t>
+  </si>
+  <si>
+    <t>0.7690,0.2499,0.0410,0.0007</t>
+  </si>
+  <si>
+    <t>0.7350,0.0433,0.0212,0.0507</t>
+  </si>
+  <si>
+    <t>0.7192,0.1518,0.0479,0.0137</t>
+  </si>
+  <si>
+    <t>0.8618,0.0449,0.0335,0.0074</t>
+  </si>
+  <si>
+    <t>0.6711,0.1658,0.0431,0.0197</t>
+  </si>
+  <si>
+    <t>0.8825,0.0448,0.0297,0.0033</t>
+  </si>
+  <si>
+    <t>0.6650,0.1364,0.1126,0.0257</t>
+  </si>
+  <si>
+    <t>0.6509,0.1318,0.0866,0.0258</t>
+  </si>
+  <si>
+    <t>0.8688,0.0606,0.0146,0.0049</t>
+  </si>
+  <si>
+    <t>0.7994,0.0953,0.0807,0.0046</t>
+  </si>
+  <si>
+    <t>0.7295,0.2236,0.0560,0.0036</t>
+  </si>
+  <si>
+    <t>0.8314,0.1261,0.0379,0.0024</t>
+  </si>
+  <si>
+    <t>0.9365,0.0244,0.0120,0.0014</t>
+  </si>
+  <si>
+    <t>0.6932,0.1984,0.0873,0.0109</t>
+  </si>
+  <si>
+    <t>0.8781,0.0432,0.0412,0.0032</t>
+  </si>
+  <si>
+    <t>0.7241,0.0901,0.0500,0.0224</t>
+  </si>
+  <si>
+    <t>0.8440,0.0589,0.0526,0.0044</t>
+  </si>
+  <si>
+    <t>0.1607,0.1961,0.8639,0.0020</t>
+  </si>
+  <si>
+    <t>0.7694,0.1049,0.0871,0.0101</t>
+  </si>
+  <si>
+    <t>0.4298,0.0160,0.7183,0.0008</t>
+  </si>
+  <si>
+    <t>0.8936,0.0040,0.1813,0.0002</t>
+  </si>
+  <si>
+    <t>0.8530,0.0191,0.1598,0.0006</t>
+  </si>
+  <si>
+    <t>0.3953,0.0373,0.5695,0.0003</t>
+  </si>
+  <si>
+    <t>0.9099,0.0151,0.0809,0.0003</t>
+  </si>
+  <si>
+    <t>0.7576,0.0092,0.3171,0.0003</t>
+  </si>
+  <si>
+    <t>0.4945,0.0382,0.6393,0.0004</t>
+  </si>
+  <si>
+    <t>0.8407,0.0794,0.0737,0.0008</t>
+  </si>
+  <si>
+    <t>0.8357,0.0451,0.1327,0.0010</t>
+  </si>
+  <si>
+    <t>0.9006,0.0534,0.0418,0.0005</t>
+  </si>
+  <si>
+    <t>0.8538,0.0893,0.0854,0.0005</t>
+  </si>
+  <si>
+    <t>0.6865,0.2558,0.1305,0.0010</t>
+  </si>
+  <si>
+    <t>0.9161,0.0262,0.0542,0.0002</t>
+  </si>
+  <si>
+    <t>0.8952,0.0561,0.0356,0.0011</t>
+  </si>
+  <si>
+    <t>0.7083,0.1631,0.1615,0.0012</t>
+  </si>
+  <si>
+    <t>0.5711,0.2866,0.1339,0.0201</t>
+  </si>
+  <si>
+    <t>0.5004,0.3602,0.1203,0.0106</t>
+  </si>
+  <si>
+    <t>0.7033,0.2165,0.0788,0.0072</t>
+  </si>
+  <si>
+    <t>0.7429,0.1316,0.0781,0.0069</t>
+  </si>
+  <si>
+    <t>0.8126,0.0369,0.0288,0.0172</t>
+  </si>
+  <si>
+    <t>0.8466,0.1315,0.0425,0.0007</t>
+  </si>
+  <si>
+    <t>0.8920,0.0529,0.0475,0.0005</t>
+  </si>
+  <si>
+    <t>0.9248,0.0162,0.0482,0.0009</t>
+  </si>
+  <si>
+    <t>0.8346,0.0604,0.1003,0.0003</t>
+  </si>
+  <si>
+    <t>0.8683,0.0169,0.1472,0.0005</t>
+  </si>
+  <si>
+    <t>0.5354,0.1695,0.4074,0.0016</t>
+  </si>
+  <si>
+    <t>0.8875,0.0201,0.0936,0.0003</t>
+  </si>
+  <si>
+    <t>0.9785,0.0068,0.0076,0.0001</t>
+  </si>
+  <si>
+    <t>0.9021,0.0144,0.0982,0.0002</t>
+  </si>
+  <si>
+    <t>0.6953,0.0661,0.2012,0.0005</t>
+  </si>
+  <si>
+    <t>0.8377,0.0222,0.0194,0.0286</t>
+  </si>
+  <si>
+    <t>0.6288,0.1852,0.0847,0.0322</t>
+  </si>
+  <si>
+    <t>0.6565,0.1359,0.0990,0.0315</t>
+  </si>
+  <si>
+    <t>0.6775,0.0937,0.0636,0.0205</t>
+  </si>
+  <si>
+    <t>0.7758,0.1471,0.0802,0.0055</t>
+  </si>
+  <si>
+    <t>0.7096,0.1694,0.0691,0.0104</t>
+  </si>
+  <si>
+    <t>0.6880,0.1162,0.1009,0.0166</t>
+  </si>
+  <si>
+    <t>0.7176,0.0986,0.0562,0.0189</t>
+  </si>
+  <si>
+    <t>0.7498,0.0540,0.2531,0.0007</t>
+  </si>
+  <si>
+    <t>0.8487,0.0445,0.0553,0.0053</t>
+  </si>
+  <si>
+    <t>0.7526,0.1120,0.1519,0.0024</t>
+  </si>
+  <si>
+    <t>0.9387,0.0033,0.0767,0.0001</t>
+  </si>
+  <si>
+    <t>0.4501,0.0316,0.6149,0.0067</t>
+  </si>
+  <si>
+    <t>0.8620,0.0187,0.1156,0.0004</t>
+  </si>
+  <si>
+    <t>0.4135,0.0654,0.5681,0.0014</t>
+  </si>
+  <si>
+    <t>0.9060,0.0322,0.0515,0.0002</t>
+  </si>
+  <si>
+    <t>0.2163,0.0110,0.8805,0.0003</t>
+  </si>
+  <si>
+    <t>0.8659,0.0079,0.1714,0.0004</t>
+  </si>
+  <si>
+    <t>0.9121,0.0113,0.0752,0.0006</t>
+  </si>
+  <si>
+    <t>0.8710,0.0715,0.0515,0.0007</t>
+  </si>
+  <si>
+    <t>0.9290,0.0157,0.0450,0.0006</t>
+  </si>
+  <si>
+    <t>0.9529,0.0184,0.0229,0.0003</t>
+  </si>
+  <si>
+    <t>0.7388,0.1252,0.0937,0.0097</t>
+  </si>
+  <si>
+    <t>0.8035,0.0472,0.0400,0.0175</t>
+  </si>
+  <si>
+    <t>0.8057,0.0369,0.0153,0.0218</t>
+  </si>
+  <si>
+    <t>0.8231,0.0555,0.0377,0.0100</t>
+  </si>
+  <si>
+    <t>0.7986,0.0422,0.0254,0.0238</t>
+  </si>
+  <si>
+    <t>0.7114,0.0734,0.0705,0.0276</t>
+  </si>
+  <si>
+    <t>0.6938,0.0785,0.0493,0.0405</t>
+  </si>
+  <si>
+    <t>0.8060,0.0606,0.0480,0.0129</t>
+  </si>
+  <si>
+    <t>0.8719,0.0100,0.1307,0.0003</t>
+  </si>
+  <si>
+    <t>0.7119,0.0346,0.2617,0.0004</t>
+  </si>
+  <si>
+    <t>0.8625,0.0099,0.1577,0.0003</t>
+  </si>
+  <si>
+    <t>0.9444,0.0144,0.0294,0.0002</t>
+  </si>
+  <si>
+    <t>0.4110,0.0770,0.5244,0.0011</t>
+  </si>
+  <si>
+    <t>0.8975,0.0140,0.0729,0.0024</t>
+  </si>
+  <si>
+    <t>0.7470,0.0255,0.3575,0.0008</t>
+  </si>
+  <si>
+    <t>0.8114,0.0310,0.1762,0.0009</t>
+  </si>
+  <si>
+    <t>0.8621,0.0410,0.0233,0.0073</t>
+  </si>
+  <si>
+    <t>0.9233,0.0323,0.0211,0.0033</t>
+  </si>
+  <si>
+    <t>0.9722,0.0062,0.0071,0.0008</t>
+  </si>
+  <si>
+    <t>0.8813,0.0181,0.0325,0.0084</t>
+  </si>
+  <si>
+    <t>0.8236,0.0632,0.0361,0.0150</t>
+  </si>
+  <si>
+    <t>0.8201,0.0799,0.0827,0.0030</t>
   </si>
 </sst>
 </file>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8187,0.0973,0.0680,0.0045</t>
-  </si>
-  <si>
-    <t>0.8564,0.0252,0.0375,0.0133</t>
-  </si>
-  <si>
-    <t>0.7707,0.1209,0.0427,0.0114</t>
-  </si>
-  <si>
-    <t>0.8351,0.0497,0.0339,0.0116</t>
-  </si>
-  <si>
-    <t>0.6331,0.1031,0.0816,0.0353</t>
-  </si>
-  <si>
-    <t>0.6205,0.1350,0.0458,0.0265</t>
-  </si>
-  <si>
-    <t>0.8069,0.0655,0.0200,0.0098</t>
-  </si>
-  <si>
-    <t>0.7788,0.1083,0.0437,0.0086</t>
-  </si>
-  <si>
-    <t>0.7699,0.0746,0.0559,0.0140</t>
-  </si>
-  <si>
-    <t>0.8732,0.0452,0.0326,0.0065</t>
-  </si>
-  <si>
-    <t>0.6999,0.1695,0.0764,0.0110</t>
-  </si>
-  <si>
-    <t>0.6766,0.1428,0.0852,0.0188</t>
-  </si>
-  <si>
-    <t>0.8800,0.0486,0.0791,0.0006</t>
-  </si>
-  <si>
-    <t>0.8083,0.1405,0.0770,0.0011</t>
-  </si>
-  <si>
-    <t>0.8704,0.0234,0.1341,0.0004</t>
-  </si>
-  <si>
-    <t>0.8839,0.0129,0.1472,0.0002</t>
-  </si>
-  <si>
-    <t>0.9110,0.0384,0.0505,0.0002</t>
-  </si>
-  <si>
-    <t>0.0740,0.9511,0.0957,0.0005</t>
-  </si>
-  <si>
-    <t>0.4337,0.5977,0.1444,0.0025</t>
-  </si>
-  <si>
-    <t>0.7850,0.1512,0.0663,0.0033</t>
-  </si>
-  <si>
-    <t>0.4678,0.5910,0.1191,0.0026</t>
-  </si>
-  <si>
-    <t>0.3307,0.7675,0.1139,0.0012</t>
-  </si>
-  <si>
-    <t>0.9549,0.0178,0.0160,0.0005</t>
-  </si>
-  <si>
-    <t>0.9266,0.0075,0.0889,0.0002</t>
-  </si>
-  <si>
-    <t>0.6497,0.0546,0.3689,0.0012</t>
-  </si>
-  <si>
-    <t>0.9436,0.0247,0.0205,0.0002</t>
-  </si>
-  <si>
-    <t>0.9533,0.0179,0.0208,0.0001</t>
-  </si>
-  <si>
-    <t>0.9050,0.0098,0.0798,0.0012</t>
-  </si>
-  <si>
-    <t>0.5590,0.0137,0.6448,0.0003</t>
-  </si>
-  <si>
-    <t>0.3337,0.7614,0.0912,0.0007</t>
-  </si>
-  <si>
-    <t>0.9332,0.0338,0.0186,0.0012</t>
-  </si>
-  <si>
-    <t>0.1112,0.0991,0.9205,0.0021</t>
-  </si>
-  <si>
-    <t>0.8399,0.0756,0.1003,0.0007</t>
-  </si>
-  <si>
-    <t>0.6950,0.2338,0.0816,0.0039</t>
-  </si>
-  <si>
-    <t>0.6811,0.1423,0.1762,0.0116</t>
-  </si>
-  <si>
-    <t>0.7461,0.1366,0.0860,0.0090</t>
-  </si>
-  <si>
-    <t>0.8694,0.1223,0.0323,0.0004</t>
-  </si>
-  <si>
-    <t>0.7258,0.0629,0.2090,0.0009</t>
-  </si>
-  <si>
-    <t>0.9597,0.0020,0.0466,0.0001</t>
-  </si>
-  <si>
-    <t>0.9135,0.0182,0.0647,0.0001</t>
-  </si>
-  <si>
-    <t>0.9469,0.0033,0.0424,0.0003</t>
-  </si>
-  <si>
-    <t>0.8961,0.0129,0.1343,0.0001</t>
-  </si>
-  <si>
-    <t>0.3350,0.7107,0.0344,0.0003</t>
-  </si>
-  <si>
-    <t>0.8332,0.0104,0.2158,0.0004</t>
-  </si>
-  <si>
-    <t>0.9185,0.0599,0.0242,0.0014</t>
-  </si>
-  <si>
-    <t>0.4900,0.6937,0.0359,0.0006</t>
-  </si>
-  <si>
-    <t>0.6866,0.4449,0.0280,0.0002</t>
-  </si>
-  <si>
-    <t>0.0319,0.9638,0.1859,0.0010</t>
-  </si>
-  <si>
-    <t>0.7280,0.0494,0.1892,0.0009</t>
-  </si>
-  <si>
-    <t>0.5121,0.0250,0.6036,0.0012</t>
-  </si>
-  <si>
-    <t>0.9395,0.0104,0.0463,0.0003</t>
-  </si>
-  <si>
-    <t>0.8562,0.0209,0.1429,0.0011</t>
-  </si>
-  <si>
-    <t>0.5821,0.0413,0.4685,0.0004</t>
-  </si>
-  <si>
-    <t>0.8198,0.0043,0.3080,0.0001</t>
-  </si>
-  <si>
-    <t>0.5405,0.2769,0.1207,0.0237</t>
-  </si>
-  <si>
-    <t>0.6832,0.1473,0.1063,0.0109</t>
-  </si>
-  <si>
-    <t>0.8510,0.0274,0.0128,0.0151</t>
-  </si>
-  <si>
-    <t>0.1389,0.5323,0.7841,0.0055</t>
-  </si>
-  <si>
-    <t>0.8124,0.0663,0.0250,0.0083</t>
-  </si>
-  <si>
-    <t>0.7447,0.0674,0.0856,0.0179</t>
-  </si>
-  <si>
-    <t>0.7005,0.1495,0.0524,0.0148</t>
-  </si>
-  <si>
-    <t>0.0337,0.7088,0.7503,0.0002</t>
-  </si>
-  <si>
-    <t>0.6217,0.0604,0.2619,0.0004</t>
-  </si>
-  <si>
-    <t>0.8064,0.0046,0.3145,0.0002</t>
-  </si>
-  <si>
-    <t>0.1134,0.7441,0.3620,0.0002</t>
-  </si>
-  <si>
-    <t>0.6605,0.0343,0.3585,0.0007</t>
-  </si>
-  <si>
-    <t>0.8663,0.1661,0.0051,0.0006</t>
-  </si>
-  <si>
-    <t>0.0148,0.9867,0.0823,0.0001</t>
-  </si>
-  <si>
-    <t>0.9471,0.0445,0.0166,0.0002</t>
-  </si>
-  <si>
-    <t>0.8196,0.0571,0.0417,0.0078</t>
-  </si>
-  <si>
-    <t>0.0323,0.5414,0.9224,0.0019</t>
-  </si>
-  <si>
-    <t>0.6819,0.3108,0.0344,0.0001</t>
-  </si>
-  <si>
-    <t>0.2091,0.6762,0.2443,0.0004</t>
-  </si>
-  <si>
-    <t>0.2104,0.8177,0.0120,0.0000</t>
-  </si>
-  <si>
-    <t>0.0948,0.8608,0.0854,0.0001</t>
-  </si>
-  <si>
-    <t>0.8745,0.0407,0.0384,0.0053</t>
-  </si>
-  <si>
-    <t>0.9483,0.0169,0.0091,0.0023</t>
-  </si>
-  <si>
-    <t>0.9109,0.0577,0.0114,0.0032</t>
-  </si>
-  <si>
-    <t>0.9101,0.0338,0.0306,0.0028</t>
-  </si>
-  <si>
-    <t>0.9504,0.0136,0.0139,0.0015</t>
-  </si>
-  <si>
-    <t>0.6975,0.0366,0.0366,0.1135</t>
-  </si>
-  <si>
-    <t>0.1610,0.4485,0.4246,0.0002</t>
-  </si>
-  <si>
-    <t>0.2421,0.1428,0.6206,0.0002</t>
-  </si>
-  <si>
-    <t>0.5130,0.0469,0.4399,0.0001</t>
-  </si>
-  <si>
-    <t>0.7966,0.0189,0.2263,0.0002</t>
-  </si>
-  <si>
-    <t>0.1769,0.7592,0.1341,0.0001</t>
-  </si>
-  <si>
-    <t>0.7881,0.0327,0.1703,0.0001</t>
-  </si>
-  <si>
-    <t>0.5716,0.2872,0.0876,0.0120</t>
-  </si>
-  <si>
-    <t>0.7027,0.0679,0.0768,0.0348</t>
-  </si>
-  <si>
-    <t>0.7233,0.0719,0.0647,0.0207</t>
-  </si>
-  <si>
-    <t>0.8212,0.0446,0.0274,0.0137</t>
-  </si>
-  <si>
-    <t>0.7519,0.0882,0.0318,0.0166</t>
-  </si>
-  <si>
-    <t>0.6525,0.2804,0.0472,0.0060</t>
-  </si>
-  <si>
-    <t>0.7759,0.0739,0.0336,0.0182</t>
-  </si>
-  <si>
-    <t>0.9060,0.0239,0.0137,0.0046</t>
-  </si>
-  <si>
-    <t>0.8079,0.0659,0.0285,0.0091</t>
-  </si>
-  <si>
-    <t>0.7107,0.0995,0.0289,0.0223</t>
-  </si>
-  <si>
-    <t>0.7873,0.0488,0.0304,0.0161</t>
-  </si>
-  <si>
-    <t>0.7710,0.0264,0.0279,0.0472</t>
-  </si>
-  <si>
-    <t>0.7395,0.0722,0.0543,0.0169</t>
-  </si>
-  <si>
-    <t>0.8720,0.0270,0.0212,0.0095</t>
-  </si>
-  <si>
-    <t>0.8438,0.0431,0.0305,0.0087</t>
-  </si>
-  <si>
-    <t>0.8476,0.0146,0.0151,0.0274</t>
-  </si>
-  <si>
-    <t>0.5343,0.0175,0.6098,0.0005</t>
-  </si>
-  <si>
-    <t>0.8768,0.0074,0.1888,0.0002</t>
-  </si>
-  <si>
-    <t>0.9091,0.0325,0.0688,0.0006</t>
-  </si>
-  <si>
-    <t>0.9303,0.0137,0.0376,0.0006</t>
-  </si>
-  <si>
-    <t>0.5438,0.5441,0.0976,0.0025</t>
-  </si>
-  <si>
-    <t>0.5572,0.4819,0.1014,0.0017</t>
-  </si>
-  <si>
-    <t>0.6262,0.3417,0.0847,0.0039</t>
-  </si>
-  <si>
-    <t>0.6224,0.3068,0.0771,0.0078</t>
-  </si>
-  <si>
-    <t>0.6667,0.3265,0.0873,0.0033</t>
-  </si>
-  <si>
-    <t>0.1804,0.8673,0.1102,0.0019</t>
-  </si>
-  <si>
-    <t>0.6755,0.2216,0.1158,0.0057</t>
-  </si>
-  <si>
-    <t>0.8920,0.0375,0.0360,0.0024</t>
-  </si>
-  <si>
-    <t>0.8658,0.0256,0.1216,0.0003</t>
-  </si>
-  <si>
-    <t>0.9465,0.0147,0.0341,0.0003</t>
-  </si>
-  <si>
-    <t>0.8932,0.1092,0.0226,0.0005</t>
-  </si>
-  <si>
-    <t>0.9315,0.0309,0.0250,0.0006</t>
-  </si>
-  <si>
-    <t>0.2289,0.8684,0.0659,0.0004</t>
-  </si>
-  <si>
-    <t>0.0698,0.9601,0.1026,0.0006</t>
-  </si>
-  <si>
-    <t>0.7774,0.1451,0.0846,0.0019</t>
-  </si>
-  <si>
-    <t>0.0587,0.9303,0.1643,0.0003</t>
-  </si>
-  <si>
-    <t>0.8813,0.0843,0.0215,0.0016</t>
-  </si>
-  <si>
-    <t>0.7126,0.1746,0.0837,0.0069</t>
-  </si>
-  <si>
-    <t>0.8027,0.1242,0.0848,0.0033</t>
-  </si>
-  <si>
-    <t>0.8292,0.0834,0.0593,0.0064</t>
-  </si>
-  <si>
-    <t>0.8997,0.0230,0.0193,0.0077</t>
-  </si>
-  <si>
-    <t>0.8077,0.0897,0.0490,0.0075</t>
-  </si>
-  <si>
-    <t>0.8453,0.0453,0.0425,0.0110</t>
-  </si>
-  <si>
-    <t>0.7453,0.0645,0.0562,0.0368</t>
-  </si>
-  <si>
-    <t>0.8756,0.0453,0.0446,0.0021</t>
-  </si>
-  <si>
-    <t>0.7879,0.1436,0.0339,0.0048</t>
-  </si>
-  <si>
-    <t>0.7637,0.0718,0.0472,0.0229</t>
-  </si>
-  <si>
-    <t>0.0610,0.8952,0.1288,0.0003</t>
-  </si>
-  <si>
-    <t>0.6416,0.0307,0.3369,0.0002</t>
-  </si>
-  <si>
-    <t>0.6978,0.0064,0.5064,0.0001</t>
-  </si>
-  <si>
-    <t>0.8955,0.0057,0.1369,0.0001</t>
-  </si>
-  <si>
-    <t>0.9147,0.0493,0.0340,0.0002</t>
-  </si>
-  <si>
-    <t>0.8882,0.0844,0.0379,0.0002</t>
-  </si>
-  <si>
-    <t>0.7900,0.0397,0.2266,0.0016</t>
-  </si>
-  <si>
-    <t>0.8322,0.1266,0.0575,0.0010</t>
-  </si>
-  <si>
-    <t>0.9662,0.0104,0.0108,0.0003</t>
-  </si>
-  <si>
-    <t>0.9026,0.0168,0.0404,0.0048</t>
-  </si>
-  <si>
-    <t>0.6872,0.4135,0.0390,0.0016</t>
-  </si>
-  <si>
-    <t>0.8585,0.0301,0.0380,0.0123</t>
-  </si>
-  <si>
-    <t>0.2228,0.3771,0.4897,0.0005</t>
-  </si>
-  <si>
-    <t>0.7403,0.0971,0.1051,0.0164</t>
-  </si>
-  <si>
-    <t>0.7030,0.2649,0.0794,0.0042</t>
-  </si>
-  <si>
-    <t>0.7097,0.1348,0.0412,0.0113</t>
-  </si>
-  <si>
-    <t>0.8013,0.1073,0.0419,0.0068</t>
-  </si>
-  <si>
-    <t>0.9085,0.0209,0.0393,0.0027</t>
-  </si>
-  <si>
-    <t>0.8044,0.1076,0.0657,0.0028</t>
-  </si>
-  <si>
-    <t>0.6956,0.1669,0.0374,0.0107</t>
-  </si>
-  <si>
-    <t>0.0263,0.6981,0.8953,0.0126</t>
-  </si>
-  <si>
-    <t>0.7605,0.1436,0.0313,0.0117</t>
-  </si>
-  <si>
-    <t>0.6105,0.1825,0.1324,0.0286</t>
-  </si>
-  <si>
-    <t>0.7042,0.2253,0.1270,0.0018</t>
-  </si>
-  <si>
-    <t>0.8306,0.0928,0.0734,0.0022</t>
-  </si>
-  <si>
-    <t>0.8855,0.0668,0.0197,0.0013</t>
-  </si>
-  <si>
-    <t>0.8952,0.0615,0.0334,0.0007</t>
-  </si>
-  <si>
-    <t>0.7813,0.1795,0.0703,0.0027</t>
-  </si>
-  <si>
-    <t>0.7690,0.2499,0.0410,0.0007</t>
-  </si>
-  <si>
-    <t>0.7350,0.0433,0.0212,0.0507</t>
-  </si>
-  <si>
-    <t>0.7192,0.1518,0.0479,0.0137</t>
-  </si>
-  <si>
-    <t>0.8618,0.0449,0.0335,0.0074</t>
-  </si>
-  <si>
-    <t>0.6711,0.1658,0.0431,0.0197</t>
-  </si>
-  <si>
-    <t>0.8825,0.0448,0.0297,0.0033</t>
-  </si>
-  <si>
-    <t>0.6650,0.1364,0.1126,0.0257</t>
-  </si>
-  <si>
-    <t>0.6509,0.1318,0.0866,0.0258</t>
-  </si>
-  <si>
-    <t>0.8688,0.0606,0.0146,0.0049</t>
-  </si>
-  <si>
-    <t>0.7994,0.0953,0.0807,0.0046</t>
-  </si>
-  <si>
-    <t>0.7295,0.2236,0.0560,0.0036</t>
-  </si>
-  <si>
-    <t>0.8314,0.1261,0.0379,0.0024</t>
-  </si>
-  <si>
-    <t>0.9365,0.0244,0.0120,0.0014</t>
-  </si>
-  <si>
-    <t>0.6932,0.1984,0.0873,0.0109</t>
-  </si>
-  <si>
-    <t>0.8781,0.0432,0.0412,0.0032</t>
-  </si>
-  <si>
-    <t>0.7241,0.0901,0.0500,0.0224</t>
-  </si>
-  <si>
-    <t>0.8440,0.0589,0.0526,0.0044</t>
-  </si>
-  <si>
-    <t>0.1607,0.1961,0.8639,0.0020</t>
-  </si>
-  <si>
-    <t>0.7694,0.1049,0.0871,0.0101</t>
-  </si>
-  <si>
-    <t>0.4298,0.0160,0.7183,0.0008</t>
-  </si>
-  <si>
-    <t>0.8936,0.0040,0.1813,0.0002</t>
-  </si>
-  <si>
-    <t>0.8530,0.0191,0.1598,0.0006</t>
-  </si>
-  <si>
-    <t>0.3953,0.0373,0.5695,0.0003</t>
-  </si>
-  <si>
-    <t>0.9099,0.0151,0.0809,0.0003</t>
-  </si>
-  <si>
-    <t>0.7576,0.0092,0.3171,0.0003</t>
-  </si>
-  <si>
-    <t>0.4945,0.0382,0.6393,0.0004</t>
-  </si>
-  <si>
-    <t>0.8407,0.0794,0.0737,0.0008</t>
-  </si>
-  <si>
-    <t>0.8357,0.0451,0.1327,0.0010</t>
-  </si>
-  <si>
-    <t>0.9006,0.0534,0.0418,0.0005</t>
-  </si>
-  <si>
-    <t>0.8538,0.0893,0.0854,0.0005</t>
-  </si>
-  <si>
-    <t>0.6865,0.2558,0.1305,0.0010</t>
-  </si>
-  <si>
-    <t>0.9161,0.0262,0.0542,0.0002</t>
-  </si>
-  <si>
-    <t>0.8952,0.0561,0.0356,0.0011</t>
-  </si>
-  <si>
-    <t>0.7083,0.1631,0.1615,0.0012</t>
-  </si>
-  <si>
-    <t>0.5711,0.2866,0.1339,0.0201</t>
-  </si>
-  <si>
-    <t>0.5004,0.3602,0.1203,0.0106</t>
-  </si>
-  <si>
-    <t>0.7033,0.2165,0.0788,0.0072</t>
-  </si>
-  <si>
-    <t>0.7429,0.1316,0.0781,0.0069</t>
-  </si>
-  <si>
-    <t>0.8126,0.0369,0.0288,0.0172</t>
-  </si>
-  <si>
-    <t>0.8466,0.1315,0.0425,0.0007</t>
-  </si>
-  <si>
-    <t>0.8920,0.0529,0.0475,0.0005</t>
-  </si>
-  <si>
-    <t>0.9248,0.0162,0.0482,0.0009</t>
-  </si>
-  <si>
-    <t>0.8346,0.0604,0.1003,0.0003</t>
-  </si>
-  <si>
-    <t>0.8683,0.0169,0.1472,0.0005</t>
-  </si>
-  <si>
-    <t>0.5354,0.1695,0.4074,0.0016</t>
-  </si>
-  <si>
-    <t>0.8875,0.0201,0.0936,0.0003</t>
-  </si>
-  <si>
-    <t>0.9785,0.0068,0.0076,0.0001</t>
-  </si>
-  <si>
-    <t>0.9021,0.0144,0.0982,0.0002</t>
-  </si>
-  <si>
-    <t>0.6953,0.0661,0.2012,0.0005</t>
-  </si>
-  <si>
-    <t>0.8377,0.0222,0.0194,0.0286</t>
-  </si>
-  <si>
-    <t>0.6288,0.1852,0.0847,0.0322</t>
-  </si>
-  <si>
-    <t>0.6565,0.1359,0.0990,0.0315</t>
-  </si>
-  <si>
-    <t>0.6775,0.0937,0.0636,0.0205</t>
-  </si>
-  <si>
-    <t>0.7758,0.1471,0.0802,0.0055</t>
-  </si>
-  <si>
-    <t>0.7096,0.1694,0.0691,0.0104</t>
-  </si>
-  <si>
-    <t>0.6880,0.1162,0.1009,0.0166</t>
-  </si>
-  <si>
-    <t>0.7176,0.0986,0.0562,0.0189</t>
-  </si>
-  <si>
-    <t>0.7498,0.0540,0.2531,0.0007</t>
-  </si>
-  <si>
-    <t>0.8487,0.0445,0.0553,0.0053</t>
-  </si>
-  <si>
-    <t>0.7526,0.1120,0.1519,0.0024</t>
-  </si>
-  <si>
-    <t>0.9387,0.0033,0.0767,0.0001</t>
-  </si>
-  <si>
-    <t>0.4501,0.0316,0.6149,0.0067</t>
-  </si>
-  <si>
-    <t>0.8620,0.0187,0.1156,0.0004</t>
-  </si>
-  <si>
-    <t>0.4135,0.0654,0.5681,0.0014</t>
-  </si>
-  <si>
-    <t>0.9060,0.0322,0.0515,0.0002</t>
-  </si>
-  <si>
-    <t>0.2163,0.0110,0.8805,0.0003</t>
-  </si>
-  <si>
-    <t>0.8659,0.0079,0.1714,0.0004</t>
-  </si>
-  <si>
-    <t>0.9121,0.0113,0.0752,0.0006</t>
-  </si>
-  <si>
-    <t>0.8710,0.0715,0.0515,0.0007</t>
-  </si>
-  <si>
-    <t>0.9290,0.0157,0.0450,0.0006</t>
-  </si>
-  <si>
-    <t>0.9529,0.0184,0.0229,0.0003</t>
-  </si>
-  <si>
-    <t>0.7388,0.1252,0.0937,0.0097</t>
-  </si>
-  <si>
-    <t>0.8035,0.0472,0.0400,0.0175</t>
-  </si>
-  <si>
-    <t>0.8057,0.0369,0.0153,0.0218</t>
-  </si>
-  <si>
-    <t>0.8231,0.0555,0.0377,0.0100</t>
-  </si>
-  <si>
-    <t>0.7986,0.0422,0.0254,0.0238</t>
-  </si>
-  <si>
-    <t>0.7114,0.0734,0.0705,0.0276</t>
-  </si>
-  <si>
-    <t>0.6938,0.0785,0.0493,0.0405</t>
-  </si>
-  <si>
-    <t>0.8060,0.0606,0.0480,0.0129</t>
-  </si>
-  <si>
-    <t>0.8719,0.0100,0.1307,0.0003</t>
-  </si>
-  <si>
-    <t>0.7119,0.0346,0.2617,0.0004</t>
-  </si>
-  <si>
-    <t>0.8625,0.0099,0.1577,0.0003</t>
-  </si>
-  <si>
-    <t>0.9444,0.0144,0.0294,0.0002</t>
-  </si>
-  <si>
-    <t>0.4110,0.0770,0.5244,0.0011</t>
-  </si>
-  <si>
-    <t>0.8975,0.0140,0.0729,0.0024</t>
-  </si>
-  <si>
-    <t>0.7470,0.0255,0.3575,0.0008</t>
-  </si>
-  <si>
-    <t>0.8114,0.0310,0.1762,0.0009</t>
-  </si>
-  <si>
-    <t>0.8621,0.0410,0.0233,0.0073</t>
-  </si>
-  <si>
-    <t>0.9233,0.0323,0.0211,0.0033</t>
-  </si>
-  <si>
-    <t>0.9722,0.0062,0.0071,0.0008</t>
-  </si>
-  <si>
-    <t>0.8813,0.0181,0.0325,0.0084</t>
-  </si>
-  <si>
-    <t>0.8236,0.0632,0.0361,0.0150</t>
-  </si>
-  <si>
-    <t>0.8201,0.0799,0.0827,0.0030</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9729,0.0065,0.0018,0.0123</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.0003,0.9994</t>
+  </si>
+  <si>
+    <t>0.9399,0.0012,0.0007,0.0576</t>
+  </si>
+  <si>
+    <t>0.8102,0.0013,0.0011,0.2574</t>
+  </si>
+  <si>
+    <t>0.9958,0.0005,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9924,0.0015,0.0001,0.0022</t>
+  </si>
+  <si>
+    <t>0.9967,0.0003,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9952,0.0010,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9802,0.0117,0.0018,0.0042</t>
+  </si>
+  <si>
+    <t>0.9914,0.0013,0.0014,0.0023</t>
+  </si>
+  <si>
+    <t>0.9958,0.0014,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.6353,0.2668,0.0887,0.0031</t>
+  </si>
+  <si>
+    <t>0.2371,0.0302,0.8060,0.0059</t>
+  </si>
+  <si>
+    <t>0.0363,0.0089,0.9758,0.0020</t>
+  </si>
+  <si>
+    <t>0.2332,0.0101,0.8545,0.0052</t>
+  </si>
+  <si>
+    <t>0.2088,0.0204,0.8113,0.0184</t>
+  </si>
+  <si>
+    <t>0.0005,0.9986,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.0034,0.9933,0.0046,0.0007</t>
+  </si>
+  <si>
+    <t>0.0696,0.9254,0.0132,0.0040</t>
+  </si>
+  <si>
+    <t>0.0006,0.9984,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.4870,0.0156,0.1231,0.3448</t>
+  </si>
+  <si>
+    <t>0.8566,0.0057,0.1021,0.0063</t>
+  </si>
+  <si>
+    <t>0.0107,0.0022,0.9867,0.0065</t>
+  </si>
+  <si>
+    <t>0.0387,0.0059,0.9627,0.0182</t>
+  </si>
+  <si>
+    <t>0.5927,0.0025,0.5853,0.0003</t>
+  </si>
+  <si>
+    <t>0.0145,0.0055,0.9873,0.0018</t>
+  </si>
+  <si>
+    <t>0.0038,0.0022,0.9899,0.0082</t>
+  </si>
+  <si>
+    <t>0.8924,0.1727,0.0064,0.0010</t>
+  </si>
+  <si>
+    <t>0.5458,0.0688,0.4495,0.0189</t>
+  </si>
+  <si>
+    <t>0.0030,0.0102,0.9935,0.0061</t>
+  </si>
+  <si>
+    <t>0.0032,0.9508,0.2391,0.0004</t>
+  </si>
+  <si>
+    <t>0.9242,0.0249,0.0097,0.0376</t>
+  </si>
+  <si>
+    <t>0.8890,0.0223,0.0674,0.0063</t>
+  </si>
+  <si>
+    <t>0.3027,0.7885,0.0027,0.0012</t>
+  </si>
+  <si>
+    <t>0.0029,0.9830,0.7199,0.0006</t>
+  </si>
+  <si>
+    <t>0.0049,0.5986,0.6560,0.0504</t>
+  </si>
+  <si>
+    <t>0.0533,0.0019,0.9437,0.0077</t>
+  </si>
+  <si>
+    <t>0.0780,0.0262,0.9253,0.0070</t>
+  </si>
+  <si>
+    <t>0.0235,0.0017,0.9782,0.0103</t>
+  </si>
+  <si>
+    <t>0.0026,0.0099,0.9951,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.9975,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.0068,0.0100,0.9849,0.0053</t>
+  </si>
+  <si>
+    <t>0.1191,0.7218,0.0064,0.5059</t>
+  </si>
+  <si>
+    <t>0.0033,0.9936,0.0110,0.0019</t>
+  </si>
+  <si>
+    <t>0.0019,0.9939,0.0178,0.0002</t>
+  </si>
+  <si>
+    <t>0.0068,0.9832,0.0366,0.0020</t>
+  </si>
+  <si>
+    <t>0.0003,0.1676,0.9900,0.0019</t>
+  </si>
+  <si>
+    <t>0.0012,0.2521,0.9901,0.0010</t>
+  </si>
+  <si>
+    <t>0.0158,0.0038,0.9851,0.0048</t>
+  </si>
+  <si>
+    <t>0.0307,0.0068,0.9686,0.0196</t>
+  </si>
+  <si>
+    <t>0.0051,0.0426,0.9825,0.0063</t>
+  </si>
+  <si>
+    <t>0.0060,0.0102,0.9896,0.0022</t>
+  </si>
+  <si>
+    <t>0.9622,0.0494,0.0033,0.0020</t>
+  </si>
+  <si>
+    <t>0.9415,0.0112,0.0488,0.0031</t>
+  </si>
+  <si>
+    <t>0.9727,0.0161,0.0046,0.0044</t>
+  </si>
+  <si>
+    <t>0.0065,0.0389,0.9851,0.0171</t>
+  </si>
+  <si>
+    <t>0.9960,0.0013,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9925,0.0035,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9325,0.0963,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.9539,0.9904,0.0000</t>
+  </si>
+  <si>
+    <t>0.0052,0.0504,0.9904,0.0007</t>
+  </si>
+  <si>
+    <t>0.0165,0.1178,0.9550,0.0066</t>
+  </si>
+  <si>
+    <t>0.0002,0.9784,0.9681,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0043,0.9958,0.0019</t>
+  </si>
+  <si>
+    <t>0.4204,0.6114,0.0196,0.0020</t>
+  </si>
+  <si>
+    <t>0.0358,0.9623,0.0057,0.0002</t>
+  </si>
+  <si>
+    <t>0.1351,0.0099,0.9235,0.0231</t>
+  </si>
+  <si>
+    <t>0.1772,0.0451,0.8785,0.0184</t>
+  </si>
+  <si>
+    <t>0.0015,0.0216,0.9939,0.0019</t>
+  </si>
+  <si>
+    <t>0.0003,0.9849,0.8886,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9920,0.7255,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.9956,0.0124,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.9752,0.8624,0.0006</t>
+  </si>
+  <si>
+    <t>0.0157,0.0012,0.0236,0.9795</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0051,0.0035,0.0004,0.9974</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.0008,0.9990</t>
+  </si>
+  <si>
+    <t>0.0020,0.0062,0.0031,0.9968</t>
+  </si>
+  <si>
+    <t>0.0018,0.0049,0.0004,0.9982</t>
+  </si>
+  <si>
+    <t>0.0002,0.9952,0.8935,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.8272,0.9687,0.0005</t>
+  </si>
+  <si>
+    <t>0.0133,0.8469,0.3816,0.0022</t>
+  </si>
+  <si>
+    <t>0.0041,0.4927,0.9378,0.0019</t>
+  </si>
+  <si>
+    <t>0.0001,0.9784,0.9701,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9160,0.9037,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9874,0.0137,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9775,0.0198,0.0015,0.0020</t>
+  </si>
+  <si>
+    <t>0.9912,0.0020,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.9850,0.0112,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.9778,0.0198,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.9841,0.0145,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9860,0.0056,0.0009,0.0034</t>
+  </si>
+  <si>
+    <t>0.9971,0.0002,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9932,0.0016,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.9972,0.0001,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9932,0.0014,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9945,0.0024,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9963,0.0012,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9970,0.0002,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.0005,0.0017,0.9958,0.0104</t>
+  </si>
+  <si>
+    <t>0.3145,0.0086,0.8382,0.0084</t>
+  </si>
+  <si>
+    <t>0.8244,0.0189,0.0349,0.1259</t>
+  </si>
+  <si>
+    <t>0.2040,0.0020,0.8583,0.0067</t>
+  </si>
+  <si>
+    <t>0.0158,0.9755,0.0043,0.0025</t>
+  </si>
+  <si>
+    <t>0.0044,0.9918,0.0111,0.0010</t>
+  </si>
+  <si>
+    <t>0.0897,0.9099,0.0113,0.0054</t>
+  </si>
+  <si>
+    <t>0.0148,0.9814,0.0060,0.0009</t>
+  </si>
+  <si>
+    <t>0.0016,0.9967,0.0034,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.9975,0.0008,0.0020</t>
+  </si>
+  <si>
+    <t>0.2433,0.7983,0.0072,0.0019</t>
+  </si>
+  <si>
+    <t>0.6045,0.0660,0.2784,0.0557</t>
+  </si>
+  <si>
+    <t>0.1724,0.0074,0.9017,0.0050</t>
+  </si>
+  <si>
+    <t>0.6825,0.0537,0.2198,0.0280</t>
+  </si>
+  <si>
+    <t>0.2544,0.0631,0.7245,0.0269</t>
+  </si>
+  <si>
+    <t>0.0150,0.0592,0.0343,0.9648</t>
+  </si>
+  <si>
+    <t>0.0052,0.9923,0.0260,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.9920,0.0200,0.0014</t>
+  </si>
+  <si>
+    <t>0.0006,0.9953,0.0066,0.0126</t>
+  </si>
+  <si>
+    <t>0.0009,0.9462,0.9246,0.0004</t>
+  </si>
+  <si>
+    <t>0.0683,0.9347,0.0915,0.0010</t>
+  </si>
+  <si>
+    <t>0.7927,0.2137,0.0593,0.0028</t>
+  </si>
+  <si>
+    <t>0.8623,0.1387,0.0323,0.0075</t>
+  </si>
+  <si>
+    <t>0.9950,0.0020,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9971,0.0001,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9948,0.0007,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9877,0.0025,0.0016,0.0031</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9934,0.0026,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9943,0.0004,0.0001,0.0034</t>
+  </si>
+  <si>
+    <t>0.9861,0.0028,0.0009,0.0041</t>
+  </si>
+  <si>
+    <t>0.0050,0.5289,0.9577,0.0009</t>
+  </si>
+  <si>
+    <t>0.0015,0.8820,0.9361,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0344,0.9934,0.0003</t>
+  </si>
+  <si>
+    <t>0.0127,0.0967,0.9667,0.0080</t>
+  </si>
+  <si>
+    <t>0.9735,0.0048,0.0117,0.0007</t>
+  </si>
+  <si>
+    <t>0.4552,0.0678,0.5745,0.0337</t>
+  </si>
+  <si>
+    <t>0.0362,0.0023,0.9843,0.0031</t>
+  </si>
+  <si>
+    <t>0.6175,0.2133,0.2612,0.0226</t>
+  </si>
+  <si>
+    <t>0.0194,0.0022,0.0019,0.9917</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0028,0.0102,0.0012,0.9971</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0015,0.9993</t>
+  </si>
+  <si>
+    <t>0.0004,0.8639,0.9526,0.0007</t>
+  </si>
+  <si>
+    <t>0.9927,0.0012,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.2843,0.7759,0.0067,0.0083</t>
+  </si>
+  <si>
+    <t>0.9832,0.0038,0.0019,0.0056</t>
+  </si>
+  <si>
+    <t>0.6813,0.3954,0.0298,0.0063</t>
+  </si>
+  <si>
+    <t>0.9917,0.0018,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.5041,0.0094,0.0684,0.4011</t>
+  </si>
+  <si>
+    <t>0.9768,0.0039,0.0013,0.0106</t>
+  </si>
+  <si>
+    <t>0.0036,0.1439,0.9773,0.0151</t>
+  </si>
+  <si>
+    <t>0.9410,0.0033,0.0020,0.0599</t>
+  </si>
+  <si>
+    <t>0.7758,0.0004,0.0007,0.3966</t>
+  </si>
+  <si>
+    <t>0.8276,0.2668,0.0047,0.0027</t>
+  </si>
+  <si>
+    <t>0.9439,0.0222,0.0086,0.0085</t>
+  </si>
+  <si>
+    <t>0.9888,0.0035,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.5091,0.3702,0.0935,0.0610</t>
+  </si>
+  <si>
+    <t>0.6931,0.0607,0.2528,0.0016</t>
+  </si>
+  <si>
+    <t>0.9570,0.0465,0.0049,0.0014</t>
+  </si>
+  <si>
+    <t>0.9908,0.0011,0.0004,0.0035</t>
+  </si>
+  <si>
+    <t>0.9904,0.0028,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9893,0.0029,0.0024,0.0022</t>
+  </si>
+  <si>
+    <t>0.9940,0.0005,0.0006,0.0024</t>
+  </si>
+  <si>
+    <t>0.9822,0.0084,0.0023,0.0030</t>
+  </si>
+  <si>
+    <t>0.9936,0.0013,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9883,0.0004,0.0010,0.0051</t>
+  </si>
+  <si>
+    <t>0.9950,0.0004,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.8921,0.0911,0.0052,0.0072</t>
+  </si>
+  <si>
+    <t>0.8640,0.1581,0.0096,0.0011</t>
+  </si>
+  <si>
+    <t>0.6865,0.4027,0.0054,0.0018</t>
+  </si>
+  <si>
+    <t>0.0697,0.1979,0.9307,0.0081</t>
+  </si>
+  <si>
+    <t>0.9888,0.0083,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9707,0.0177,0.0053,0.0023</t>
+  </si>
+  <si>
+    <t>0.9847,0.0107,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.9830,0.0057,0.0021,0.0056</t>
+  </si>
+  <si>
+    <t>0.0012,0.0009,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.9847,0.0115,0.0026,0.0013</t>
+  </si>
+  <si>
+    <t>0.0076,0.0083,0.9892,0.0037</t>
+  </si>
+  <si>
+    <t>0.0131,0.0354,0.9838,0.0012</t>
+  </si>
+  <si>
+    <t>0.0215,0.0009,0.9901,0.0010</t>
+  </si>
+  <si>
+    <t>0.0004,0.0897,0.9930,0.0024</t>
+  </si>
+  <si>
+    <t>0.0164,0.0135,0.9852,0.0022</t>
+  </si>
+  <si>
+    <t>0.0266,0.0049,0.9780,0.0033</t>
+  </si>
+  <si>
+    <t>0.0013,0.0016,0.9964,0.0013</t>
+  </si>
+  <si>
+    <t>0.1042,0.0403,0.8817,0.0281</t>
+  </si>
+  <si>
+    <t>0.7852,0.0065,0.1907,0.0094</t>
+  </si>
+  <si>
+    <t>0.1869,0.0234,0.8646,0.0198</t>
+  </si>
+  <si>
+    <t>0.0993,0.6458,0.2495,0.0029</t>
+  </si>
+  <si>
+    <t>0.0901,0.1060,0.8493,0.0027</t>
+  </si>
+  <si>
+    <t>0.3909,0.1243,0.4583,0.0065</t>
+  </si>
+  <si>
+    <t>0.6453,0.0390,0.3688,0.0210</t>
+  </si>
+  <si>
+    <t>0.1285,0.0789,0.8862,0.0071</t>
+  </si>
+  <si>
+    <t>0.0457,0.9578,0.0035,0.0010</t>
+  </si>
+  <si>
+    <t>0.1088,0.9214,0.0032,0.0011</t>
+  </si>
+  <si>
+    <t>0.9022,0.1394,0.0012,0.0018</t>
+  </si>
+  <si>
+    <t>0.9909,0.0082,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.0567,0.9393,0.0024,0.0062</t>
+  </si>
+  <si>
+    <t>0.9459,0.0190,0.0271,0.0024</t>
+  </si>
+  <si>
+    <t>0.8729,0.0251,0.1231,0.0060</t>
+  </si>
+  <si>
+    <t>0.2512,0.0415,0.0237,0.7262</t>
+  </si>
+  <si>
+    <t>0.3893,0.0087,0.8276,0.0016</t>
+  </si>
+  <si>
+    <t>0.2435,0.0295,0.5409,0.2614</t>
+  </si>
+  <si>
+    <t>0.0123,0.0136,0.9671,0.0404</t>
+  </si>
+  <si>
+    <t>0.0155,0.2382,0.9482,0.0027</t>
+  </si>
+  <si>
+    <t>0.2958,0.0370,0.6419,0.0709</t>
+  </si>
+  <si>
+    <t>0.0126,0.0136,0.9784,0.0022</t>
+  </si>
+  <si>
+    <t>0.0136,0.1212,0.9589,0.0062</t>
+  </si>
+  <si>
+    <t>0.9908,0.0006,0.0001,0.0062</t>
+  </si>
+  <si>
+    <t>0.9937,0.0017,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.8829,0.1177,0.0065,0.0157</t>
+  </si>
+  <si>
+    <t>0.9851,0.0059,0.0007,0.0047</t>
+  </si>
+  <si>
+    <t>0.9344,0.0432,0.0144,0.0168</t>
+  </si>
+  <si>
+    <t>0.9914,0.0050,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9863,0.0059,0.0007,0.0023</t>
+  </si>
+  <si>
+    <t>0.9940,0.0014,0.0004,0.0020</t>
+  </si>
+  <si>
+    <t>0.0169,0.0115,0.9881,0.0030</t>
+  </si>
+  <si>
+    <t>0.7020,0.1030,0.1300,0.0589</t>
+  </si>
+  <si>
+    <t>0.8809,0.0363,0.0719,0.0142</t>
+  </si>
+  <si>
+    <t>0.0030,0.0015,0.9973,0.0004</t>
+  </si>
+  <si>
+    <t>0.0060,0.0045,0.9691,0.0404</t>
+  </si>
+  <si>
+    <t>0.0395,0.2105,0.9147,0.0039</t>
+  </si>
+  <si>
+    <t>0.0007,0.0011,0.9984,0.0009</t>
+  </si>
+  <si>
+    <t>0.0276,0.0365,0.9276,0.0110</t>
+  </si>
+  <si>
+    <t>0.0010,0.0031,0.9949,0.0036</t>
+  </si>
+  <si>
+    <t>0.0011,0.0027,0.9930,0.0090</t>
+  </si>
+  <si>
+    <t>0.1156,0.0435,0.8243,0.0290</t>
+  </si>
+  <si>
+    <t>0.5183,0.0111,0.5357,0.0269</t>
+  </si>
+  <si>
+    <t>0.5330,0.0087,0.4380,0.0441</t>
+  </si>
+  <si>
+    <t>0.9603,0.0037,0.0218,0.0022</t>
+  </si>
+  <si>
+    <t>0.9917,0.0029,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.9831,0.0092,0.0023,0.0026</t>
+  </si>
+  <si>
+    <t>0.9936,0.0034,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9865,0.0053,0.0022,0.0035</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9954,0.0011,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9953,0.0017,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9879,0.0083,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.0065,0.0537,0.9766,0.0024</t>
+  </si>
+  <si>
+    <t>0.0041,0.3160,0.9792,0.0006</t>
+  </si>
+  <si>
+    <t>0.0036,0.0072,0.9928,0.0010</t>
+  </si>
+  <si>
+    <t>0.0265,0.0050,0.9701,0.0071</t>
+  </si>
+  <si>
+    <t>0.0303,0.0771,0.9424,0.0100</t>
+  </si>
+  <si>
+    <t>0.4689,0.0056,0.2721,0.1884</t>
+  </si>
+  <si>
+    <t>0.0167,0.0018,0.9910,0.0009</t>
+  </si>
+  <si>
+    <t>0.0234,0.0054,0.8239,0.2574</t>
+  </si>
+  <si>
+    <t>0.5796,0.0007,0.0035,0.5323</t>
+  </si>
+  <si>
+    <t>0.0044,0.0124,0.0019,0.9952</t>
+  </si>
+  <si>
+    <t>0.0055,0.0032,0.0005,0.9970</t>
+  </si>
+  <si>
+    <t>0.0027,0.0005,0.0002,0.9988</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9410,0.0138,0.0058,0.0282</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2180,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,10 +2600,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2628,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,10 +2684,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,10 +2866,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2908,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,10 +3468,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3482,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3496,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3510,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3902,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4605,7 @@
         <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4798,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4812,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4826,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5039,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5064,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5176,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5403,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
